--- a/data/daily/2026-10/2026-10-21.xlsx
+++ b/data/daily/2026-10/2026-10-21.xlsx
@@ -1170,14 +1170,89 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="381000" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>2</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>3</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>4</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="342900" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1192,17 +1267,17 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>2</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="457200" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="2" name="Image 2" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId2"/>
+      <row>5</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1217,17 +1292,17 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>3</row>
+      <row>6</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="3" name="Image 3" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId3"/>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1242,135 +1317,60 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>4</row>
+      <row>7</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="342900" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>8</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="342900" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>9</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="4" name="Image 4" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>5</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="342900" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="5" name="Image 5" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>6</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="342900" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="6" name="Image 6" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>7</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="342900" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="7" name="Image 7" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>8</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="342900" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="8" name="Image 8" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>9</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="342900" cy="457200"/>
     <pic>
       <nvPicPr>
         <cNvPr id="9" name="Image 9" descr="Picture"/>
@@ -1425,52 +1425,127 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="1028700" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1028700" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1028700" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="933450" cy="1238250"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>3</col>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1238250" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="2" name="Image 2" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>4</col>
+    <ext cx="1028700" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
@@ -1478,154 +1553,79 @@
     <ext cx="1028700" cy="1238250"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="3" name="Image 3" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="933450" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="933450" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="1028700" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="4" name="Image 4" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>6</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="933450" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="5" name="Image 5" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>7</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="933450" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="6" name="Image 6" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="933450" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="7" name="Image 7" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>9</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="933450" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="8" name="Image 8" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>10</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="933450" cy="1238250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="9" name="Image 9" descr="Picture"/>
@@ -2596,16 +2596,16 @@
         <v>4</v>
       </c>
       <c r="J2" t="n">
-        <v>16320</v>
+        <v>16321</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>피로 해소 및 활력 증진 — 섭취 후 피로가 덜하고 기운이 나는 건강 개선 효과 체감</t>
+          <t>확실한 피로 회복 효과 — 아침 복용 시 피로감이 덜하고 기운이 나는 느낌임</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>선물용 높은 만족도 — 생일이나 응원 선물로 주고받기 좋고 실용적임</t>
+          <t>선물용으로 높은 만족도 — 실용적이고 마음을 전하기 좋아 선물용으로 감동을 줌</t>
         </is>
       </c>
       <c r="M2" t="inlineStr"/>
@@ -2655,15 +2655,19 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>부담 없는 맛과 목넘김 — 신맛이 강하지 않고 맛이 좋아 편안하게 섭취 가능함</t>
+          <t>간편한 일체형 복용 — 액상과 정제가 함께 들어 있어 하루 영양을 간편하게 챙김</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>간편한 복합 영양 구성 — 액상과 정제가 함께 들어 있어 바쁜 일상 속 활력 섭취에 용이함</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
+          <t>부담 없이 맛있는 풍미 — 시지 않고 맛이 좋아 매일 거부감 없이 섭취 가능함</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>고급스러운 패키지 — 포장이 꼼꼼하고 고급스러워 선물용으로 제격임</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
@@ -2706,19 +2710,23 @@
         <v>4</v>
       </c>
       <c r="J4" t="n">
-        <v>3416</v>
+        <v>3417</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>우수한 체력 회복 체감 — 피로감이 줄어들고 지친 체력을 보충하는 데 도움을 줌</t>
+          <t>넉넉한 대용량 구성 — 30개입 구성으로 오랫동안 꾸준히 챙겨 먹기 좋음</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>넉넉한 용량과 고급 패키지 — 30개입의 넉넉한 수량과 깔끔한 포장으로 선물용으로 적합함</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr"/>
+          <t>선물에 적합한 예쁜 포장 — 패키지와 포장이 예쁘고 마음을 전하기에 훌륭함</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>체력 관리에 유용함 — 체력이 떨어지거나 수술 후 회복 시 챙겨 먹기 좋음</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
@@ -2765,15 +2773,19 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>맛있고 쫄깃한 젤리 제형 — 과일 맛에 과하게 달지 않고 씹는 맛이 좋아 온 가족이 즐기기 좋음</t>
+          <t>맛있는 과일맛 젤리 — 과일맛의 말랑한 젤리 형태로 간식처럼 맛있게 먹기 좋음</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>물 없는 간편한 섭취 — 바쁜 아침에도 물 없이 간식처럼 씹어 먹을 수 있어 편리함</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
+          <t>물 없이 씹는 편의성 — 바쁜 아침에도 물 없이 씹어서 간편하게 영양을 챙김</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>안전 용기 디자인 — 안전캡이 적용되어 아이가 있는 집에서도 안심하고 보관함</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
@@ -2820,15 +2832,19 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>빠른 피로 회복 도움 — 환절기 컨디션 관리 및 일상 피로를 푸는 데 만족스러움</t>
+          <t>빠른 피로 회복 체감 — 피로 해소에 도움이 되고 환절기 컨디션 관리에 효과적임</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>우수한 휴대 및 복용 편의 — 간편하게 들고 다니며 챙겨 먹기 좋은 제품 구성임</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
+          <t>휴대 및 복용 용이성 — 개별 구성으로 휴대하기 좋고 언제 어디서나 먹기 편함</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>실용적인 선물 선택 — 받는 사람이 반가워하고 기분 좋아지는 센스 있는 선물임</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
@@ -2871,35 +2887,35 @@
         <v>4</v>
       </c>
       <c r="J7" t="n">
-        <v>1784</v>
+        <v>1786</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>즉각적인 활력 충전 — 섭취 후 피로가 줄고 가뿐해지는 에너지 회복 체감</t>
+          <t>우수한 에너지 충전 — 복용 후 피로가 풀리고 하루 마무리가 가뿐해짐</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>버튼 혼합의 재미와 위생 — 버튼을 눌러 가루를 섞어 마시는 독특하고 위생적인 방식임</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr"/>
+          <t>고급스러운 선물 패키지 — 포장이 예쁘고 고급스러워 주변에 선물하기에 적합함</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>신기한 혼합형 디자인 — 버튼을 눌러 섞어 마시는 형태라 재미있고 간편함</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>가루 섞임 후 쌉쌀한 맛 — 분말이 혼합되면서 약간의 쓴맛이나 약 맛이 느껴짐</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>섭취 방식 안내 필요 — 버튼 누르는 방식을 모르면 액상만 마실 우려가 있음</t>
-        </is>
-      </c>
+          <t>생소한 복용 방법 — 뚜껑을 눌러 섞어 마시는 방식으로 첫 복용 시 생소할 수 있음</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
     </row>
     <row r="8" ht="38" customHeight="1">
       <c r="B8" t="inlineStr">
         <is>
-          <t>비타민C/항산화</t>
+          <t>멀티비타민/종합비타민</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -2907,58 +2923,58 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>고함량 비타민C 고려은단 메가도스C 3000 100포 / 분말비타민C</t>
+          <t>명품 비타민 뉴트리포유 듀얼+ 이뮨 종합 멀티비타민&amp;미네랄 7입+2입 증정 - 선물하기 단독 에디션</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>고려은단</t>
+          <t>뉴트리포유</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>24,900원</t>
+          <t>19,900원</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/3252731</t>
+          <t>https://gift.kakao.com/product/10056171</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260909091732_b68718856ae342d0b37c3e36916af86b.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260219100848_1c2cc8073bd44eaab9f09d6b8fb8f34c.jpg</t>
         </is>
       </c>
       <c r="I8" t="n">
         <v>4</v>
       </c>
       <c r="J8" t="n">
-        <v>975</v>
+        <v>8757</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>합리적인 가격과 신속 배송 — 행사 가격으로 저렴하게 구매 가능하며 배송이 매우 빠름</t>
+          <t>기운이 나는 피로 개선 — 피곤할 때 섭취하면 기운이 나고 다음 날 컨디션이 좋아짐</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>믿음직한 고함량 원료 — 영국산 퀄리씨 원료를 사용해 믿고 메가도스 요법으로 섭취함</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>강렬한 신맛 섭취 부담 — 분말 형태 특유의 신맛이 매우 강해 삼키기 부담스러울 수 있음</t>
-        </is>
-      </c>
+          <t>섭취하기 편한 액상 — 마시는 액상 타입이라 간편하고 쉽게 챙겨 먹을 수 있음</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>반가운 선물용 상품 — 건강을 챙길 수 있는 실용적이고 기분 좋은 선물임</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
     </row>
     <row r="9" ht="38" customHeight="1">
       <c r="B9" t="inlineStr">
         <is>
-          <t>멀티비타민/종합비타민</t>
+          <t>비타민C/항산화</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -2966,47 +2982,51 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>명품 비타민 뉴트리포유 듀얼+ 이뮨 종합 멀티비타민&amp;미네랄 7입+2입 증정 - 선물하기 단독 에디션</t>
+          <t>고함량 비타민C 고려은단 메가도스C 3000 100포 / 분말비타민C</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>뉴트리포유</t>
+          <t>고려은단</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>19,900원</t>
+          <t>24,900원</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/10056171</t>
+          <t>https://gift.kakao.com/product/3252731</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260219100848_1c2cc8073bd44eaab9f09d6b8fb8f34c.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260909091732_b68718856ae342d0b37c3e36916af86b.jpg</t>
         </is>
       </c>
       <c r="I9" t="n">
         <v>4</v>
       </c>
       <c r="J9" t="n">
-        <v>8756</v>
+        <v>975</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>다음 날 달라지는 컨디션 — 섭취 후 다음 날 기운이 나고 활력 충전에 도움을 줌</t>
+          <t>착한 가격과 빠른 배송 — 행사 가격으로 저렴하게 구매 가능하며 배송이 매우 빠름</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>마시는 형태의 복용 편의 — 액상 타입이라 물 없이도 한 번에 간편하게 섭취 가능함</t>
+          <t>믿을 수 있는 품질 — 영국산 원료를 사용한 메가도스 용량으로 신뢰도가 높음</t>
         </is>
       </c>
       <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>강한 신맛의 부담 — 분말 제형이라 신맛이 매우 강해 호불호가 갈릴 수 있음</t>
+        </is>
+      </c>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
     </row>
@@ -3052,25 +3072,21 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>확실한 피로 개선 체감 — 꾸준히 복용 시 혓바늘 완화 및 피로 누적 방지에 탁월함</t>
+          <t>뛰어난 피로 개선 효과 — 혓바늘 완화 등 피로 회복에 빠르게 작용하여 삶의 질을 높임</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>편리한 올인원 영양 보충 — 비타민과 미네랄을 한 포로 해결해 챙겨 먹는 번거로움이 없음</t>
+          <t>편리한 올인원 제형 — 액상과 정제가 함께 들어 있어 한 번에 여러 영양을 챙김</t>
         </is>
       </c>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>짧은 잔여 소비기한 — 할인 상품의 경우 유통기한이 예상보다 짧아 섭취 기간이 촉박함</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>다소 부담스러운 정가 — 효과는 우수하지만 평소 가격대가 다소 높게 느껴짐</t>
-        </is>
-      </c>
+          <t>짧은 유통기한 아쉬움 — 할인 구매 시 남은 유통기한이 다소 짧게 느껴짐</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
     </row>
     <row r="11" ht="38" customHeight="1">
@@ -3115,15 +3131,19 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>체력 증진 및 피로 완화 — 아침에 복용 시 하루 종일 활력이 유지되고 피로가 덜함</t>
+          <t>하루 종일 유지되는 활력 — 아침 복용 시 하루 종일 피로가 줄고 활력이 생김</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>정제 액상 분리형 구조 — 알약과 액상이 따로 나뉘어 있어 위생적이고 취향껏 섭취 가능함</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr"/>
+          <t>위생적인 분리 구성 — 액상과 알약이 분리되어 원하는 방식으로 위생적 섭취 가능함</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>간편한 올인원 챙김 — 비타민과 미네랄을 한 번에 해결할 수 있어 편리함</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
@@ -3139,49 +3159,53 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>[라이브][그레인온] 골드 카무트 브랜드밀효소G 3개월분+10포증정(총100포) +파로저당단백칩+고단백질바 증정</t>
+          <t>부족함 없이 인기상품만 넣은 [한끼통살]닭가슴살 Non-stop 올인원패키지 36팩+ [증정]보냉백</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>그레인온</t>
+          <t>한끼통살</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>22,900원</t>
+          <t>53,900원</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/13180362</t>
+          <t>https://gift.kakao.com/product/12201735</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20261021072912_8fb7b30cf81541ca9f53e68b4f7f8fb6.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20261020120042_199291b1836c4a999ea96c64351fbe0f.jpg</t>
         </is>
       </c>
       <c r="I12" t="n">
         <v>4</v>
       </c>
       <c r="J12" t="n">
-        <v>943</v>
+        <v>29</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>속 편한 소화 및 배변 도움 — 식후 복용 시 가스가 차지 않고 변비 개선에 효과적임</t>
+          <t>다양한 맛과 구성 제공 — 36가지 다양한 맛으로 구성되어 다이어트 중 질리지 않음</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>풍성한 덤과 사은품 구성 — 단백칩과 견과류바 등 추가 증정 혜택이 푸짐함</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr"/>
+          <t>부드럽고 간편한 조리 — 살코기가 부드럽고 간단히 데워 한 끼를 해결하기 좋음</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>신속한 누락 대응 — 수량 누락 문의 시 빠르게 재발송하여 대응해 줌</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>냄새와 맛에 대한 호불호 — 기존 프리미엄 제품 대비 냄새와 맛이 입에 맞지 않을 수 있음</t>
+          <t>초기 배송 누락 발생 — 일부 수량이 누락되어 따로 문의 후 받아야 하는 불편이 있음</t>
         </is>
       </c>
       <c r="O12" t="inlineStr"/>
@@ -3208,7 +3232,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>46,900원</t>
+          <t>43,900원</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -3229,18 +3253,22 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>편안한 소화와 배변 활동 — 식후 섭취 시 소화가 잘되고 배변 활동 촉진에 도움을 줌</t>
+          <t>소화 및 배변 활동 도움 — 식후 소화가 잘 되고 배변 활동 개선에 효과적임</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>고급스러운 포장과 증정품 — 패키지가 정성스럽고 견과류바 구성이 알차 선물하기 좋음</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr"/>
+          <t>푸짐한 사은품 증정 — 견과류바 등 구성 사은품이 넉넉하게 제공되어 만족스러움</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>고급스러운 포장 상태 — 정성스럽고 고급스러운 포장으로 선물용에 적합함</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>기존과 달라진 맛의 변화 — 이전 제품에 비해 맛이 진해지거나 달라져 섭취 시 생소함</t>
+          <t>이전 대비 진해진 맛 — 기존 제품보다 맛이 다소 찐해져 기존 이용자가 당황할 수 있음</t>
         </is>
       </c>
       <c r="O13" t="inlineStr"/>
@@ -3249,7 +3277,7 @@
     <row r="14" ht="38" customHeight="1">
       <c r="B14" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -3257,66 +3285,58 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>[한끼통살] 닭가슴살 한달 식단 패키지 30팩+(증정)보냉백+소시지꼬치 오리지널맛 1개</t>
+          <t>[그레인온] 골드 카무트 브랜드밀효소G 3개월분+10포증정(총100포) +파로저당견과류바 증정</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>한끼통살</t>
+          <t>그레인온</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>45,900원</t>
+          <t>22,900원</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/11566779</t>
+          <t>https://gift.kakao.com/product/13180362</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260429112212_3e1db89ad7174b6989286381ae7257c6.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20261021101500_a33c07ee9dfe4879b427c57a18d9ce91.jpg</t>
         </is>
       </c>
       <c r="I14" t="n">
         <v>4</v>
       </c>
       <c r="J14" t="n">
-        <v>159</v>
+        <v>943</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>맛있는 양념과 든든한 포만감 — 떡볶이맛 등 소스가 맛있고 한 팩으로도 포만감이 높음</t>
+          <t>속 더부룩함 및 변비 개선 — 가스가 차지 않고 소화가 잘 되어 속이 편안해짐</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>질리지 않는 다채로운 구성 — 맛과 종류가 다양해 식단 관리 시 물리지 않고 섭취 가능함</t>
+          <t>풍성한 추가 사은품 — 견과류바와 단백칩 등 기대 이상의 덤이 함께 제공됨</t>
         </is>
       </c>
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
-          <t>배송 중 일부 제품 해동 — 수령 시 제품이 약간 녹아서 도착하는 아쉬움이 있음</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>구성 누락 및 미흡한 대응 — 지정된 구성과 다르게 오배송되었으나 문의 응답이 지연됨</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>다소 강한 양념 간 — 생각보다 간이 센 편이라 단독으로 먹기엔 짤 수 있음</t>
-        </is>
-      </c>
+          <t>호불호 갈리는 맛과 향 — 프리미엄 제품에 비해 맛과 냄새가 다소 아쉽게 느껴짐</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
     </row>
     <row r="15" ht="38" customHeight="1">
       <c r="B15" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -3324,54 +3344,62 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>리센느 에디션 캡슐레이션 효소 1.8g 2개월분 (5종 중 택1)</t>
+          <t>[한끼통살] 닭가슴살 한달 식단 패키지 30팩+(증정)보냉백+소시지꼬치 오리지널맛 1개</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>그레인온</t>
+          <t>한끼통살</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>26,900원</t>
+          <t>45,900원</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/14208051</t>
+          <t>https://gift.kakao.com/product/11566779</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20261001090325_278bae1c2a364ec2a56a72260f627cdc.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260429112212_3e1db89ad7174b6989286381ae7257c6.jpg</t>
         </is>
       </c>
       <c r="I15" t="n">
         <v>4</v>
       </c>
       <c r="J15" t="n">
-        <v>269</v>
+        <v>159</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>거부감 없는 맛있는 풍미 — 말차 등 다양한 맛으로 구성되어 출출할 때 간식처럼 먹기 좋음</t>
+          <t>뛰어난 포만감과 맛 — 한 개만 먹어도 포만감이 오래 가며 소스 맛이 뛰어남</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>만족스러운 포토카드 굿즈 — 리센느 포토카드와 단백질바 증정 퀄리티가 우수함</t>
+          <t>만족스러운 구성과 혜택 — 할인된 가격에 예쁜 보냉백 사은품까지 제공받음</t>
         </is>
       </c>
       <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>구성품 배송 오답 문제 — 선택한 구성과 다르게 중복 제품이 오고 문의 처리가 미흡함</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>다소 강한 간 처리 — 단독으로 먹기에 간이 세서 밥과 함께 먹어야 적당함</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr"/>
     </row>
     <row r="16" ht="38" customHeight="1">
       <c r="B16" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -3379,46 +3407,50 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>[한끼통살] 단백질 든든형 닭가슴살 21일식단관리+ (증정)현미크리스피 닭가슴살 오리지널 1개</t>
+          <t>리센느 에디션 캡슐레이션 효소 1.8g 2개월분 (5종 중 택1)</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>한끼통살</t>
+          <t>그레인온</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>33,000원</t>
+          <t>26,900원</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/12860133</t>
+          <t>https://gift.kakao.com/product/14208051</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260821134612_62bbe99621d6408d9e7e793b67d6e079.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20261001090325_278bae1c2a364ec2a56a72260f627cdc.jpg</t>
         </is>
       </c>
       <c r="I16" t="n">
         <v>4</v>
       </c>
       <c r="J16" t="n">
-        <v>70</v>
+        <v>269</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>촉촉하고 부드러운 육질 — 퍽퍽하지 않고 부드러워 먹기 편하며 식감이 우수함</t>
+          <t>맛있게 먹는 효소 — 맛이 우수하여 출출할 때 간식용으로 먹기 좋음</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>간편한 전자레인지 조리 — 데우기만 하면 바로 완성되어 식사 대용으로 간편함</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr"/>
+          <t>훌륭한 굿즈 포토카드 — 포토카드 퀄리티가 높고 단백질바 사은품 구성이 알참</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>신속하고 안전한 배송 — 배송이 빠르게 이루어져 만족도가 높음</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr"/>
@@ -3426,7 +3458,7 @@
     <row r="17" ht="38" customHeight="1">
       <c r="B17" t="inlineStr">
         <is>
-          <t>피부/미용</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -3434,58 +3466,58 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>"선물하기 1등 콜라겐" 아일로 타입1 콜라겐 비오틴 앰플 28일분 오간자 에디션+ 앰플 2입 추가 증정</t>
+          <t>[한끼통살] 단백질 든든형 닭가슴살 21일식단관리+ (증정)현미크리스피 닭가슴살 오리지널 1개</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>아일로</t>
+          <t>한끼통살</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>65,900원</t>
+          <t>33,000원</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/4965835</t>
+          <t>https://gift.kakao.com/product/12860133</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260928091559_44d67bbfbab644e3bc688b7716d83f5d.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260821134612_62bbe99621d6408d9e7e793b67d6e079.jpg</t>
         </is>
       </c>
       <c r="I17" t="n">
         <v>4</v>
       </c>
       <c r="J17" t="n">
-        <v>758</v>
+        <v>70</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>고급스러운 오간자 패키지 — 선물용 가방과 포장이 매우 예뻐 언박싱 만족도가 높음</t>
+          <t>촉촉한 식감과 다양한 맛 — 닭가슴살이 촉촉하고 여러 맛으로 구성되어 질리지 않음</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>피부 보습과 탄력 기대 — 비오틴과 콜라겐이 들어 있어 피부가 촉촉해지고 피로감이 덜함</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>정가 구매 시 비용 부담 — 효과는 만족스러우나 가격이 다소 비싸 할인 구매를 노려야 함</t>
-        </is>
-      </c>
+          <t>전자레인지 간편 조리 — 전자레인지로 쉽게 데워 먹을 수 있어 식단 관리에 유용함</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>빠르고 튼튼한 배송 — 포장이 꼼꼼하고 빠른 배송으로 전달됨</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr"/>
     </row>
     <row r="18" ht="38" customHeight="1">
       <c r="B18" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>피부/미용</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -3493,54 +3525,58 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>[단독] 알디콤Plus 숙취해소제 선물세트 (5포입x3개)</t>
+          <t>"선물하기 1등 콜라겐" 아일로 타입1 콜라겐 비오틴 앰플 28일분 오간자 에디션+ 앰플 2입 추가 증정</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>알디콤</t>
+          <t>아일로</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>33,200원</t>
+          <t>65,900원</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/12064702</t>
+          <t>https://gift.kakao.com/product/4965835</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260827134326_6543fa160cfd4c4294103fd47b3d0a12.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260928091559_44d67bbfbab644e3bc688b7716d83f5d.jpg</t>
         </is>
       </c>
       <c r="I18" t="n">
         <v>4</v>
       </c>
       <c r="J18" t="n">
-        <v>93</v>
+        <v>758</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>확실한 숙취 경감 효과 — 음주 전후 복용 시 다음 날 숙취와 속 쓰림이 덜함</t>
+          <t>고급스러운 패키지 포장 — 포장과 플리츠백 구성이 예쁘고 고급스러움</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>스틱형 간편 휴대 설계 — 가방이나 주머니에 쏙 들어가는 스틱 파우치로 휴대가 편리함</t>
+          <t>피부 촉촉함 및 피로 완화 — 맛이 좋고 꾸준히 마시면 피부가 촉촉해지고 피로가 덜함</t>
         </is>
       </c>
       <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>부담스러운 가격대 — 가격이 다소 비싸 할인 행사 시에만 구매하게 됨</t>
+        </is>
+      </c>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr"/>
     </row>
     <row r="19" ht="38" customHeight="1">
       <c r="B19" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -3548,58 +3584,58 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>[추가증정] 셀렉스 프로핏 맛있는 완전단백질 250ml 36팩 딸기초코/모카초콜릿/밀크바닐라/바나나 택1+2팩</t>
+          <t>[단독] 알디콤Plus 숙취해소제 선물세트 (5포입x3개)</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>셀렉스</t>
+          <t>알디콤</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>52,900원</t>
+          <t>33,200원</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/13550310</t>
+          <t>https://gift.kakao.com/product/12064702</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260907094540_f1360cf6411b4c4783cd2ebdea51f85c.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260827134326_6543fa160cfd4c4294103fd47b3d0a12.jpg</t>
         </is>
       </c>
       <c r="I19" t="n">
         <v>4</v>
       </c>
       <c r="J19" t="n">
-        <v>31</v>
+        <v>94</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>비린 맛 없는 달콤한 풍미 — 프로틴 특유의 비릿함 없이 바나나우유처럼 맛있게 섭취 가능함</t>
+          <t>우수한 휴대성과 개별 포장 — 스틱 형태라 가방이나 주머니에 넣어 다니기 편함</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>속 편한 락토프리 설계 — 유당불내증 걱정 없이 속이 편안해 아침 식사 대용으로 적합함</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>일부 맛의 다소 느끼함 — 밀크바나나 등 특정 플레이버는 입맛에 따라 다소 느끼할 수 있음</t>
-        </is>
-      </c>
+          <t>확실한 숙취 해소 효과 — 다음 날 아침 숙취가 적고 속이 훨씬 개운함</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>물 없이 편한 액상 제형 — 짜 먹는 액상 타입이며 거부감 없는 맛으로 섭취하기 편함</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr"/>
     </row>
     <row r="20" ht="38" customHeight="1">
       <c r="B20" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -3607,46 +3643,50 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>[혼합 18개입] 셀렉스 프로핏 맛있는 완전단백질 250ml 18팩 딸기초코/모카초콜릿/밀크바닐라/바나나+2팩</t>
+          <t>[그레인온] 골드 파로효소 캡슐레이션 3개월(+선물포장)+쇼핑백 +떠먹는 스초생(기프티콘) +그린캡슐레이션효소 증정</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>셀렉스</t>
+          <t>그레인온</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>28,900원</t>
+          <t>64,900원</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/13550266</t>
+          <t>https://gift.kakao.com/product/13255641</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260907094509_48a662610e174029823081c612ed4755.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20261021073227_092124ed988646b681660bae0e309ffa.jpg</t>
         </is>
       </c>
       <c r="I20" t="n">
         <v>4</v>
       </c>
       <c r="J20" t="n">
-        <v>218</v>
+        <v>33</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>음료처럼 깔끔한 맛 — 특유의 텁텁함 없이 초코우유나 라떼를 마시는 듯함</t>
+          <t>달콤한 고구마 맛 제형 — 고소하고 달달한 고구마 맛이라 거부감 없이 섭취 가능함</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>운동 후 만족스러운 포만감 — 운동 직후 마시면 허기짐을 달래주고 배가 든든하게 유지됨</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr"/>
+          <t>빠른 소화 및 속 편함 — 식후 더부룩함이 가라앉고 빠르게 소화가 잘 됨</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>선물용 쇼핑백 증정 — 포장이 고급스럽고 쇼핑백이 동봉되어 선물용으로 좋음</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr"/>
@@ -3662,47 +3702,55 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>[골라담기] 식단관리 크런틴 크런치볼 단백질쉐이크 2박스 50g x 10포</t>
+          <t>[추가증정] 셀렉스 프로핏 맛있는 완전단백질 250ml 36팩 딸기초코/모카초콜릿/밀크바닐라/바나나 택1+2팩</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>크런틴</t>
+          <t>셀렉스</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>58,200원</t>
+          <t>52,900원</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/14408269</t>
+          <t>https://gift.kakao.com/product/13550310</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20261019115059_ac5fb17ea3454c8a91aacd4c95250543.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260907094540_f1360cf6411b4c4783cd2ebdea51f85c.jpg</t>
         </is>
       </c>
       <c r="I21" t="n">
         <v>4</v>
       </c>
       <c r="J21" t="n">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>바삭한 토핑과 높은 포만감 — 크런치볼이 풍부하게 씹혀 식감이 좋고 포만감이 오래감</t>
+          <t>비린 맛 없는 깔끔함 — 단백질 특유의 비린 맛이 없고 맛이 뛰어남</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>맹물 혼합 시에도 진한 맛 — 우유 없이 찬물만 넣고 흔들어 마셔도 충분히 달콤하고 맛있음</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
+          <t>속이 편한 락토프리 — 유당 불내증 걱정 없이 속 편하게 마실 수 있음</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>사은품 증정 및 빠른 배송 — 프로틴바 증정과 신속한 배송이 만족스러움</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>일부 맛의 약간의 느끼함 — 밀크바나나 맛 등의 경우 개인에 따라 다소 느끼할 수 있음</t>
+        </is>
+      </c>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr"/>
     </row>
@@ -3847,12 +3895,12 @@
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
+          <t>멀티비타민/종합비타민</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
           <t>비타민C/항산화</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>멀티비타민/종합비타민</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
@@ -3904,12 +3952,12 @@
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
+          <t>뉴트리포유</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
           <t>고려은단</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>뉴트리포유</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
@@ -3961,12 +4009,12 @@
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
+          <t>명품 비타민 뉴트리포유 듀얼+ 이뮨 종합 멀티비타민&amp;미네랄 7입+2입 증정 - 선물하기 단독 에디션</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
           <t>고함량 비타민C 고려은단 메가도스C 3000 100포 / 분말비타민C</t>
-        </is>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>명품 비타민 뉴트리포유 듀얼+ 이뮨 종합 멀티비타민&amp;미네랄 7입+2입 증정 - 선물하기 단독 에디션</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
@@ -4024,13 +4072,13 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>16320</v>
+        <v>16321</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>15659</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>3416</v>
+        <v>3417</v>
       </c>
       <c r="F7" s="3" t="n">
         <v>6529</v>
@@ -4039,13 +4087,13 @@
         <v>828</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>1784</v>
+        <v>1786</v>
       </c>
       <c r="I7" s="3" t="n">
+        <v>8757</v>
+      </c>
+      <c r="J7" s="3" t="n">
         <v>975</v>
-      </c>
-      <c r="J7" s="3" t="n">
-        <v>8756</v>
       </c>
       <c r="K7" s="3" t="n">
         <v>129</v>
@@ -4054,7 +4102,7 @@
         <v>840</v>
       </c>
     </row>
-    <row r="8" ht="60" customHeight="1">
+    <row r="8" ht="90" customHeight="1">
       <c r="B8" s="1" t="inlineStr">
         <is>
           <t>긍정리뷰</t>
@@ -4062,66 +4110,73 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>피로 해소 및 활력 증진 — 섭취 후 피로가 덜하고 기운이 나는 건강 개선 효과 체감
-선물용 높은 만족도 — 생일이나 응원 선물로 주고받기 좋고 실용적임</t>
+          <t>확실한 피로 회복 효과 — 아침 복용 시 피로감이 덜하고 기운이 나는 느낌임
+선물용으로 높은 만족도 — 실용적이고 마음을 전하기 좋아 선물용으로 감동을 줌</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>부담 없는 맛과 목넘김 — 신맛이 강하지 않고 맛이 좋아 편안하게 섭취 가능함
-간편한 복합 영양 구성 — 액상과 정제가 함께 들어 있어 바쁜 일상 속 활력 섭취에 용이함</t>
+          <t>간편한 일체형 복용 — 액상과 정제가 함께 들어 있어 하루 영양을 간편하게 챙김
+부담 없이 맛있는 풍미 — 시지 않고 맛이 좋아 매일 거부감 없이 섭취 가능함
+고급스러운 패키지 — 포장이 꼼꼼하고 고급스러워 선물용으로 제격임</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>우수한 체력 회복 체감 — 피로감이 줄어들고 지친 체력을 보충하는 데 도움을 줌
-넉넉한 용량과 고급 패키지 — 30개입의 넉넉한 수량과 깔끔한 포장으로 선물용으로 적합함</t>
+          <t>넉넉한 대용량 구성 — 30개입 구성으로 오랫동안 꾸준히 챙겨 먹기 좋음
+선물에 적합한 예쁜 포장 — 패키지와 포장이 예쁘고 마음을 전하기에 훌륭함
+체력 관리에 유용함 — 체력이 떨어지거나 수술 후 회복 시 챙겨 먹기 좋음</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>맛있고 쫄깃한 젤리 제형 — 과일 맛에 과하게 달지 않고 씹는 맛이 좋아 온 가족이 즐기기 좋음
-물 없는 간편한 섭취 — 바쁜 아침에도 물 없이 간식처럼 씹어 먹을 수 있어 편리함</t>
+          <t>맛있는 과일맛 젤리 — 과일맛의 말랑한 젤리 형태로 간식처럼 맛있게 먹기 좋음
+물 없이 씹는 편의성 — 바쁜 아침에도 물 없이 씹어서 간편하게 영양을 챙김
+안전 용기 디자인 — 안전캡이 적용되어 아이가 있는 집에서도 안심하고 보관함</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>빠른 피로 회복 도움 — 환절기 컨디션 관리 및 일상 피로를 푸는 데 만족스러움
-우수한 휴대 및 복용 편의 — 간편하게 들고 다니며 챙겨 먹기 좋은 제품 구성임</t>
+          <t>빠른 피로 회복 체감 — 피로 해소에 도움이 되고 환절기 컨디션 관리에 효과적임
+휴대 및 복용 용이성 — 개별 구성으로 휴대하기 좋고 언제 어디서나 먹기 편함
+실용적인 선물 선택 — 받는 사람이 반가워하고 기분 좋아지는 센스 있는 선물임</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>즉각적인 활력 충전 — 섭취 후 피로가 줄고 가뿐해지는 에너지 회복 체감
-버튼 혼합의 재미와 위생 — 버튼을 눌러 가루를 섞어 마시는 독특하고 위생적인 방식임</t>
+          <t>우수한 에너지 충전 — 복용 후 피로가 풀리고 하루 마무리가 가뿐해짐
+고급스러운 선물 패키지 — 포장이 예쁘고 고급스러워 주변에 선물하기에 적합함
+신기한 혼합형 디자인 — 버튼을 눌러 섞어 마시는 형태라 재미있고 간편함</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>합리적인 가격과 신속 배송 — 행사 가격으로 저렴하게 구매 가능하며 배송이 매우 빠름
-믿음직한 고함량 원료 — 영국산 퀄리씨 원료를 사용해 믿고 메가도스 요법으로 섭취함</t>
+          <t>기운이 나는 피로 개선 — 피곤할 때 섭취하면 기운이 나고 다음 날 컨디션이 좋아짐
+섭취하기 편한 액상 — 마시는 액상 타입이라 간편하고 쉽게 챙겨 먹을 수 있음
+반가운 선물용 상품 — 건강을 챙길 수 있는 실용적이고 기분 좋은 선물임</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>다음 날 달라지는 컨디션 — 섭취 후 다음 날 기운이 나고 활력 충전에 도움을 줌
-마시는 형태의 복용 편의 — 액상 타입이라 물 없이도 한 번에 간편하게 섭취 가능함</t>
+          <t>착한 가격과 빠른 배송 — 행사 가격으로 저렴하게 구매 가능하며 배송이 매우 빠름
+믿을 수 있는 품질 — 영국산 원료를 사용한 메가도스 용량으로 신뢰도가 높음</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>확실한 피로 개선 체감 — 꾸준히 복용 시 혓바늘 완화 및 피로 누적 방지에 탁월함
-편리한 올인원 영양 보충 — 비타민과 미네랄을 한 포로 해결해 챙겨 먹는 번거로움이 없음</t>
+          <t>뛰어난 피로 개선 효과 — 혓바늘 완화 등 피로 회복에 빠르게 작용하여 삶의 질을 높임
+편리한 올인원 제형 — 액상과 정제가 함께 들어 있어 한 번에 여러 영양을 챙김</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>체력 증진 및 피로 완화 — 아침에 복용 시 하루 종일 활력이 유지되고 피로가 덜함
-정제 액상 분리형 구조 — 알약과 액상이 따로 나뉘어 있어 위생적이고 취향껏 섭취 가능함</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="60" customHeight="1">
+          <t>하루 종일 유지되는 활력 — 아침 복용 시 하루 종일 피로가 줄고 활력이 생김
+위생적인 분리 구성 — 액상과 알약이 분리되어 원하는 방식으로 위생적 섭취 가능함
+간편한 올인원 챙김 — 비타민과 미네랄을 한 번에 해결할 수 있어 편리함</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
       <c r="B9" s="1" t="inlineStr">
         <is>
           <t>부정리뷰</t>
@@ -4134,20 +4189,18 @@
       <c r="G9" s="3" t="inlineStr"/>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>가루 섞임 후 쌉쌀한 맛 — 분말이 혼합되면서 약간의 쓴맛이나 약 맛이 느껴짐
-섭취 방식 안내 필요 — 버튼 누르는 방식을 모르면 액상만 마실 우려가 있음</t>
-        </is>
-      </c>
-      <c r="I9" s="3" t="inlineStr">
-        <is>
-          <t>강렬한 신맛 섭취 부담 — 분말 형태 특유의 신맛이 매우 강해 삼키기 부담스러울 수 있음</t>
-        </is>
-      </c>
-      <c r="J9" s="3" t="inlineStr"/>
+          <t>생소한 복용 방법 — 뚜껑을 눌러 섞어 마시는 방식으로 첫 복용 시 생소할 수 있음</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr"/>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>강한 신맛의 부담 — 분말 제형이라 신맛이 매우 강해 호불호가 갈릴 수 있음</t>
+        </is>
+      </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>짧은 잔여 소비기한 — 할인 상품의 경우 유통기한이 예상보다 짧아 섭취 기간이 촉박함
-다소 부담스러운 정가 — 효과는 우수하지만 평소 가격대가 다소 높게 느껴짐</t>
+          <t>짧은 유통기한 아쉬움 — 할인 구매 시 남은 유통기한이 다소 짧게 느껴짐</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr"/>
@@ -4190,12 +4243,12 @@
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
+          <t>19,900원</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
           <t>24,900원</t>
-        </is>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>19,900원</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
@@ -4358,37 +4411,37 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
           <t>다이어트/체중관리</t>
         </is>
       </c>
-      <c r="F15" s="3" t="inlineStr">
+      <c r="G15" s="3" t="inlineStr">
         <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="G15" s="3" t="inlineStr">
+      <c r="H15" s="3" t="inlineStr">
         <is>
           <t>다이어트/체중관리</t>
         </is>
       </c>
-      <c r="H15" s="3" t="inlineStr">
+      <c r="I15" s="3" t="inlineStr">
         <is>
           <t>피부/미용</t>
         </is>
       </c>
-      <c r="I15" s="3" t="inlineStr">
+      <c r="J15" s="3" t="inlineStr">
         <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t>다이어트/체중관리</t>
-        </is>
-      </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
@@ -4405,52 +4458,52 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
+          <t>한끼통살</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
           <t>그레인온</t>
         </is>
       </c>
-      <c r="D16" s="3" t="inlineStr">
+      <c r="E16" s="3" t="inlineStr">
         <is>
           <t>그레인온</t>
         </is>
       </c>
-      <c r="E16" s="3" t="inlineStr">
+      <c r="F16" s="3" t="inlineStr">
         <is>
           <t>한끼통살</t>
         </is>
       </c>
-      <c r="F16" s="3" t="inlineStr">
+      <c r="G16" s="3" t="inlineStr">
         <is>
           <t>그레인온</t>
         </is>
       </c>
-      <c r="G16" s="3" t="inlineStr">
+      <c r="H16" s="3" t="inlineStr">
         <is>
           <t>한끼통살</t>
         </is>
       </c>
-      <c r="H16" s="3" t="inlineStr">
+      <c r="I16" s="3" t="inlineStr">
         <is>
           <t>아일로</t>
         </is>
       </c>
-      <c r="I16" s="3" t="inlineStr">
+      <c r="J16" s="3" t="inlineStr">
         <is>
           <t>알디콤</t>
         </is>
       </c>
-      <c r="J16" s="3" t="inlineStr">
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>그레인온</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="inlineStr">
         <is>
           <t>셀렉스</t>
-        </is>
-      </c>
-      <c r="K16" s="3" t="inlineStr">
-        <is>
-          <t>셀렉스</t>
-        </is>
-      </c>
-      <c r="L16" s="3" t="inlineStr">
-        <is>
-          <t>크런틴</t>
         </is>
       </c>
     </row>
@@ -4462,7 +4515,7 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>[라이브][그레인온] 골드 카무트 브랜드밀효소G 3개월분+10포증정(총100포) +파로저당단백칩+고단백질바 증정</t>
+          <t>부족함 없이 인기상품만 넣은 [한끼통살]닭가슴살 Non-stop 올인원패키지 36팩+ [증정]보냉백</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
@@ -4472,42 +4525,42 @@
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
+          <t>[그레인온] 골드 카무트 브랜드밀효소G 3개월분+10포증정(총100포) +파로저당견과류바 증정</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
           <t>[한끼통살] 닭가슴살 한달 식단 패키지 30팩+(증정)보냉백+소시지꼬치 오리지널맛 1개</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
+      <c r="G17" s="3" t="inlineStr">
         <is>
           <t>리센느 에디션 캡슐레이션 효소 1.8g 2개월분 (5종 중 택1)</t>
         </is>
       </c>
-      <c r="G17" s="3" t="inlineStr">
+      <c r="H17" s="3" t="inlineStr">
         <is>
           <t>[한끼통살] 단백질 든든형 닭가슴살 21일식단관리+ (증정)현미크리스피 닭가슴살 오리지널 1개</t>
         </is>
       </c>
-      <c r="H17" s="3" t="inlineStr">
+      <c r="I17" s="3" t="inlineStr">
         <is>
           <t>"선물하기 1등 콜라겐" 아일로 타입1 콜라겐 비오틴 앰플 28일분 오간자 에디션+ 앰플 2입 추가 증정</t>
         </is>
       </c>
-      <c r="I17" s="3" t="inlineStr">
+      <c r="J17" s="3" t="inlineStr">
         <is>
           <t>[단독] 알디콤Plus 숙취해소제 선물세트 (5포입x3개)</t>
         </is>
       </c>
-      <c r="J17" s="3" t="inlineStr">
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>[그레인온] 골드 파로효소 캡슐레이션 3개월(+선물포장)+쇼핑백 +떠먹는 스초생(기프티콘) +그린캡슐레이션효소 증정</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
         <is>
           <t>[추가증정] 셀렉스 프로핏 맛있는 완전단백질 250ml 36팩 딸기초코/모카초콜릿/밀크바닐라/바나나 택1+2팩</t>
-        </is>
-      </c>
-      <c r="K17" s="3" t="inlineStr">
-        <is>
-          <t>[혼합 18개입] 셀렉스 프로핏 맛있는 완전단백질 250ml 18팩 딸기초코/모카초콜릿/밀크바닐라/바나나+2팩</t>
-        </is>
-      </c>
-      <c r="L17" s="3" t="inlineStr">
-        <is>
-          <t>[골라담기] 식단관리 크런틴 크런치볼 단백질쉐이크 2박스 50g x 10포</t>
         </is>
       </c>
     </row>
@@ -4555,37 +4608,37 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>943</v>
+        <v>29</v>
       </c>
       <c r="D19" s="3" t="n">
         <v>1757</v>
       </c>
       <c r="E19" s="3" t="n">
+        <v>943</v>
+      </c>
+      <c r="F19" s="3" t="n">
         <v>159</v>
       </c>
-      <c r="F19" s="3" t="n">
+      <c r="G19" s="3" t="n">
         <v>269</v>
       </c>
-      <c r="G19" s="3" t="n">
+      <c r="H19" s="3" t="n">
         <v>70</v>
       </c>
-      <c r="H19" s="3" t="n">
+      <c r="I19" s="3" t="n">
         <v>758</v>
       </c>
-      <c r="I19" s="3" t="n">
-        <v>93</v>
-      </c>
       <c r="J19" s="3" t="n">
+        <v>94</v>
+      </c>
+      <c r="K19" s="3" t="n">
+        <v>33</v>
+      </c>
+      <c r="L19" s="3" t="n">
         <v>31</v>
       </c>
-      <c r="K19" s="3" t="n">
-        <v>218</v>
-      </c>
-      <c r="L19" s="3" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="20" ht="60" customHeight="1">
+    </row>
+    <row r="20" ht="90" customHeight="1">
       <c r="B20" s="1" t="inlineStr">
         <is>
           <t>긍정리뷰</t>
@@ -4593,66 +4646,73 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>속 편한 소화 및 배변 도움 — 식후 복용 시 가스가 차지 않고 변비 개선에 효과적임
-풍성한 덤과 사은품 구성 — 단백칩과 견과류바 등 추가 증정 혜택이 푸짐함</t>
+          <t>다양한 맛과 구성 제공 — 36가지 다양한 맛으로 구성되어 다이어트 중 질리지 않음
+부드럽고 간편한 조리 — 살코기가 부드럽고 간단히 데워 한 끼를 해결하기 좋음
+신속한 누락 대응 — 수량 누락 문의 시 빠르게 재발송하여 대응해 줌</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>편안한 소화와 배변 활동 — 식후 섭취 시 소화가 잘되고 배변 활동 촉진에 도움을 줌
-고급스러운 포장과 증정품 — 패키지가 정성스럽고 견과류바 구성이 알차 선물하기 좋음</t>
+          <t>소화 및 배변 활동 도움 — 식후 소화가 잘 되고 배변 활동 개선에 효과적임
+푸짐한 사은품 증정 — 견과류바 등 구성 사은품이 넉넉하게 제공되어 만족스러움
+고급스러운 포장 상태 — 정성스럽고 고급스러운 포장으로 선물용에 적합함</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>맛있는 양념과 든든한 포만감 — 떡볶이맛 등 소스가 맛있고 한 팩으로도 포만감이 높음
-질리지 않는 다채로운 구성 — 맛과 종류가 다양해 식단 관리 시 물리지 않고 섭취 가능함</t>
+          <t>속 더부룩함 및 변비 개선 — 가스가 차지 않고 소화가 잘 되어 속이 편안해짐
+풍성한 추가 사은품 — 견과류바와 단백칩 등 기대 이상의 덤이 함께 제공됨</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>거부감 없는 맛있는 풍미 — 말차 등 다양한 맛으로 구성되어 출출할 때 간식처럼 먹기 좋음
-만족스러운 포토카드 굿즈 — 리센느 포토카드와 단백질바 증정 퀄리티가 우수함</t>
+          <t>뛰어난 포만감과 맛 — 한 개만 먹어도 포만감이 오래 가며 소스 맛이 뛰어남
+만족스러운 구성과 혜택 — 할인된 가격에 예쁜 보냉백 사은품까지 제공받음</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>촉촉하고 부드러운 육질 — 퍽퍽하지 않고 부드러워 먹기 편하며 식감이 우수함
-간편한 전자레인지 조리 — 데우기만 하면 바로 완성되어 식사 대용으로 간편함</t>
+          <t>맛있게 먹는 효소 — 맛이 우수하여 출출할 때 간식용으로 먹기 좋음
+훌륭한 굿즈 포토카드 — 포토카드 퀄리티가 높고 단백질바 사은품 구성이 알참
+신속하고 안전한 배송 — 배송이 빠르게 이루어져 만족도가 높음</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>고급스러운 오간자 패키지 — 선물용 가방과 포장이 매우 예뻐 언박싱 만족도가 높음
-피부 보습과 탄력 기대 — 비오틴과 콜라겐이 들어 있어 피부가 촉촉해지고 피로감이 덜함</t>
+          <t>촉촉한 식감과 다양한 맛 — 닭가슴살이 촉촉하고 여러 맛으로 구성되어 질리지 않음
+전자레인지 간편 조리 — 전자레인지로 쉽게 데워 먹을 수 있어 식단 관리에 유용함
+빠르고 튼튼한 배송 — 포장이 꼼꼼하고 빠른 배송으로 전달됨</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>확실한 숙취 경감 효과 — 음주 전후 복용 시 다음 날 숙취와 속 쓰림이 덜함
-스틱형 간편 휴대 설계 — 가방이나 주머니에 쏙 들어가는 스틱 파우치로 휴대가 편리함</t>
+          <t>고급스러운 패키지 포장 — 포장과 플리츠백 구성이 예쁘고 고급스러움
+피부 촉촉함 및 피로 완화 — 맛이 좋고 꾸준히 마시면 피부가 촉촉해지고 피로가 덜함</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>비린 맛 없는 달콤한 풍미 — 프로틴 특유의 비릿함 없이 바나나우유처럼 맛있게 섭취 가능함
-속 편한 락토프리 설계 — 유당불내증 걱정 없이 속이 편안해 아침 식사 대용으로 적합함</t>
+          <t>우수한 휴대성과 개별 포장 — 스틱 형태라 가방이나 주머니에 넣어 다니기 편함
+확실한 숙취 해소 효과 — 다음 날 아침 숙취가 적고 속이 훨씬 개운함
+물 없이 편한 액상 제형 — 짜 먹는 액상 타입이며 거부감 없는 맛으로 섭취하기 편함</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>음료처럼 깔끔한 맛 — 특유의 텁텁함 없이 초코우유나 라떼를 마시는 듯함
-운동 후 만족스러운 포만감 — 운동 직후 마시면 허기짐을 달래주고 배가 든든하게 유지됨</t>
+          <t>달콤한 고구마 맛 제형 — 고소하고 달달한 고구마 맛이라 거부감 없이 섭취 가능함
+빠른 소화 및 속 편함 — 식후 더부룩함이 가라앉고 빠르게 소화가 잘 됨
+선물용 쇼핑백 증정 — 포장이 고급스럽고 쇼핑백이 동봉되어 선물용으로 좋음</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>바삭한 토핑과 높은 포만감 — 크런치볼이 풍부하게 씹혀 식감이 좋고 포만감이 오래감
-맹물 혼합 시에도 진한 맛 — 우유 없이 찬물만 넣고 흔들어 마셔도 충분히 달콤하고 맛있음</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="90" customHeight="1">
+          <t>비린 맛 없는 깔끔함 — 단백질 특유의 비린 맛이 없고 맛이 뛰어남
+속이 편한 락토프리 — 유당 불내증 걱정 없이 속 편하게 마실 수 있음
+사은품 증정 및 빠른 배송 — 프로틴바 증정과 신속한 배송이 만족스러움</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="60" customHeight="1">
       <c r="B21" s="1" t="inlineStr">
         <is>
           <t>부정리뷰</t>
@@ -4660,36 +4720,39 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>냄새와 맛에 대한 호불호 — 기존 프리미엄 제품 대비 냄새와 맛이 입에 맞지 않을 수 있음</t>
+          <t>초기 배송 누락 발생 — 일부 수량이 누락되어 따로 문의 후 받아야 하는 불편이 있음</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>기존과 달라진 맛의 변화 — 이전 제품에 비해 맛이 진해지거나 달라져 섭취 시 생소함</t>
+          <t>이전 대비 진해진 맛 — 기존 제품보다 맛이 다소 찐해져 기존 이용자가 당황할 수 있음</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>배송 중 일부 제품 해동 — 수령 시 제품이 약간 녹아서 도착하는 아쉬움이 있음
-구성 누락 및 미흡한 대응 — 지정된 구성과 다르게 오배송되었으나 문의 응답이 지연됨
-다소 강한 양념 간 — 생각보다 간이 센 편이라 단독으로 먹기엔 짤 수 있음</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr"/>
+          <t>호불호 갈리는 맛과 향 — 프리미엄 제품에 비해 맛과 냄새가 다소 아쉽게 느껴짐</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>구성품 배송 오답 문제 — 선택한 구성과 다르게 중복 제품이 오고 문의 처리가 미흡함
+다소 강한 간 처리 — 단독으로 먹기에 간이 세서 밥과 함께 먹어야 적당함</t>
+        </is>
+      </c>
       <c r="G21" s="3" t="inlineStr"/>
-      <c r="H21" s="3" t="inlineStr">
-        <is>
-          <t>정가 구매 시 비용 부담 — 효과는 만족스러우나 가격이 다소 비싸 할인 구매를 노려야 함</t>
-        </is>
-      </c>
-      <c r="I21" s="3" t="inlineStr"/>
-      <c r="J21" s="3" t="inlineStr">
-        <is>
-          <t>일부 맛의 다소 느끼함 — 밀크바나나 등 특정 플레이버는 입맛에 따라 다소 느끼할 수 있음</t>
-        </is>
-      </c>
+      <c r="H21" s="3" t="inlineStr"/>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>부담스러운 가격대 — 가격이 다소 비싸 할인 행사 시에만 구매하게 됨</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="inlineStr"/>
       <c r="K21" s="3" t="inlineStr"/>
-      <c r="L21" s="3" t="inlineStr"/>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t>일부 맛의 약간의 느끼함 — 밀크바나나 맛 등의 경우 개인에 따라 다소 느끼할 수 있음</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="B22" s="1" t="inlineStr">
@@ -4699,52 +4762,52 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
+          <t>53,900원</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>43,900원</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
           <t>22,900원</t>
         </is>
       </c>
-      <c r="D22" s="3" t="inlineStr">
-        <is>
-          <t>46,900원</t>
-        </is>
-      </c>
-      <c r="E22" s="3" t="inlineStr">
+      <c r="F22" s="3" t="inlineStr">
         <is>
           <t>45,900원</t>
         </is>
       </c>
-      <c r="F22" s="3" t="inlineStr">
+      <c r="G22" s="3" t="inlineStr">
         <is>
           <t>26,900원</t>
         </is>
       </c>
-      <c r="G22" s="3" t="inlineStr">
+      <c r="H22" s="3" t="inlineStr">
         <is>
           <t>33,000원</t>
         </is>
       </c>
-      <c r="H22" s="3" t="inlineStr">
+      <c r="I22" s="3" t="inlineStr">
         <is>
           <t>65,900원</t>
         </is>
       </c>
-      <c r="I22" s="3" t="inlineStr">
+      <c r="J22" s="3" t="inlineStr">
         <is>
           <t>33,200원</t>
         </is>
       </c>
-      <c r="J22" s="3" t="inlineStr">
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t>64,900원</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
         <is>
           <t>52,900원</t>
-        </is>
-      </c>
-      <c r="K22" s="3" t="inlineStr">
-        <is>
-          <t>28,900원</t>
-        </is>
-      </c>
-      <c r="L22" s="3" t="inlineStr">
-        <is>
-          <t>58,200원</t>
         </is>
       </c>
     </row>
@@ -4934,7 +4997,7 @@
     <row r="2" ht="38" customHeight="1">
       <c r="B2" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>마그네슘</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -4942,12 +5005,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>[강력한 상쾌함] [신혜선 PICK] 동국제약 프로폴리스 프레쉬볼 스트롱민트 20캡슐 20일분</t>
+          <t>대웅제약 마그네슘 30정 30일분</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -4957,47 +5020,39 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=610911101&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000128&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260907/BQeSyYNH21gmMrEclYYV610911101_00_01BQeSyYNH21gmMrEclYYV.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/DZz3h5SxY2J2FqaEB9qZ600000128_00_00DZz3h5SxY2J2FqaEB9qZ.png</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="J2" t="n">
-        <v>320</v>
+        <v>7031</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>입안 가득 빠른 상쾌함 — 터뜨리는 순간 강한 민트 향이 퍼져 입안이 즉각 개운해짐</t>
+          <t>합리적인 가격과 성분 — 가격이 저렴하고 알찬 성분 구성으로 꾸준히 먹기 좋음</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>뛰어난 가성비와 휴대성 — 저렴한 가격으로 언제 어디서나 구취 관리가 가능함</t>
+          <t>빠른 배송 서비스 — 배송 처리가 빨라 빠르게 수령 가능함</t>
         </is>
       </c>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>다소 짧은 향 지속력 — 순간적인 상쾌함은 좋으나 향의 지속 시간이 다소 짧음</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>외피 젤리의 이질감 — 입안에 남는 말캉한 캡슐 껍질 식감에 이질감을 느낄 수 있음</t>
-        </is>
-      </c>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
     </row>
     <row r="3" ht="38" customHeight="1">
       <c r="B3" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>혈행</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -5005,62 +5060,50 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>[식후 혈당] 동화 배러크런치 바나바 요구르트맛 30정 10일분</t>
+          <t>대웅제약 코엔자임 Q10 30캡슐 30일분</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>동화약품</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>3,000원</t>
+          <t>5,000원</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=601678608&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000144&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260825/oxNqPxCfU3Tre5j0PQQk601678608_00_02oxNqPxCfU3Tre5j0PQQk.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/OqDM0kpIHoqFD3okk28W600000144_00_00OqDM0kpIHoqFD3okk28W.png</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="J3" t="n">
-        <v>181</v>
+        <v>7498</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>맛있는 요구르트맛 캔디 — 달콤한 요구르트 맛으로 간식 먹듯이 맛있게 씹어 먹음</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>식후 나른함 완화 도움 — 점심 식사 후 졸릴 때 씹어 먹으며 잠을 깨기에 좋음</t>
-        </is>
-      </c>
+          <t>뛰어난 가성비 — 가격 대비 성능이 뛰어나 자주 부담 없이 구매함</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>생각보다 딱딱한 식감 — 정제가 다소 딱딱해 치아에 무리가 갈 수 있어 주의 필요함</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>혈당 조절 체감의 한계 — 단기간 섭취로는 뚜렷한 기능성 효과를 체감하기 어려움</t>
-        </is>
-      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
     </row>
     <row r="4" ht="38" customHeight="1">
       <c r="B4" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>루테인/눈건강</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -5068,7 +5111,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>대웅제약 녹차카테킨 30정 30일분</t>
+          <t>대웅제약 루테인 30정 30일분</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -5078,33 +5121,33 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000136&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000126&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250408/5KgtE2Z5pfS6P1gIBIIh600000136_00_005KgtE2Z5pfS6P1gIBIIh.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/u8Kxfk5gV3uvRKBRNTM6600000126_00_00u8Kxfk5gV3uvRKBRNTM6.png</t>
         </is>
       </c>
       <c r="I4" t="n">
         <v>4.8</v>
       </c>
       <c r="J4" t="n">
-        <v>3988</v>
+        <v>4290</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>부담 없는 가성비 가격 — 매우 저렴한 가격에 구매할 수 있어 꾸준히 복용하기 좋음</t>
+          <t>높은 가성비와 만족도 — 저렴한 가격으로 꾸준한 눈 건강 관리에 도움이 됨</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>식후 체중 유지 관리 — 식사 직후 섭취하여 일상적인 체중 유지에 보조 역할을 함</t>
+          <t>신속한 배송 — 주문 후 배송이 빠름</t>
         </is>
       </c>
       <c r="M4" t="inlineStr"/>
@@ -5115,7 +5158,7 @@
     <row r="5" ht="38" customHeight="1">
       <c r="B5" t="inlineStr">
         <is>
-          <t>혈행</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -5123,54 +5166,62 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>대웅제약 코엔자임 Q10 30캡슐 30일분</t>
+          <t>[산뜻한 상쾌함] [신혜선 PICK] 동국제약 프로폴리스 프레쉬볼 레몬＆민트 20캡슐 20일분</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000144&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=610911102&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250408/OqDM0kpIHoqFD3okk28W600000144_00_00OqDM0kpIHoqFD3okk28W.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260907/D3MtLfS4wvzyyoiG4ppT610911102_00_01D3MtLfS4wvzyyoiG4ppT.jpg</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J5" t="n">
-        <v>7489</v>
+        <v>337</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>목넘김 편한 적당한 크기 — 알약 크기가 크지 않아 목에 걸리지 않고 편하게 삼켜짐</t>
+          <t>입안의 산뜻한 상쾌함 — 입안이 텁텁할 때 한 개씩 먹으면 개운해짐</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>오후 시간대 피로 완화 — 한 달간 꾸준히 섭취 시 오후에 덜 지치고 피로가 줄어듦</t>
+          <t>구취 제거 도움 — 입냄새 완화에 유용함</t>
         </is>
       </c>
       <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>입안에 남는 잔여 캡슐 — 캡슐 녹은 후 입안에 껍질만 남고 상쾌함 지속이 짧음</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>삼켜야 하는 강한 맛 — 터트려 먹으면 맛이 강해 그냥 삼켜야 하는 불편함이 있음</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr"/>
     </row>
     <row r="6" ht="38" customHeight="1">
       <c r="B6" t="inlineStr">
         <is>
-          <t>마그네슘</t>
+          <t>비타민D</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -5178,12 +5229,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>자연관 리프레쉬 마그네슘＆L-테아닌 4병 4일분</t>
+          <t>대웅제약 칼슘 마그네슘 비타민D 60정 30일분</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>자연관</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -5193,39 +5244,43 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=032627142&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000148&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260612/IiBr1SI0rlUycwbkaeGq032627142_00_01IiBr1SI0rlUycwbkaeGq.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/a7ohwSe3ShJimhwztOOK600000148_00_00a7ohwSe3ShJimhwztOOK.png</t>
         </is>
       </c>
       <c r="I6" t="n">
         <v>4.8</v>
       </c>
       <c r="J6" t="n">
-        <v>341</v>
+        <v>3747</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>부드러운 입면과 숙면 — 취침 전 마시면 잠드는 과정이 부드럽고 기상 시 개운함</t>
+          <t>편리한 복합 성분 보충 — 칼슘, 마그네슘, 비타민D를 한 알로 간편하게 섭취함</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>마시는 형태의 빠른 흡수 — 액상형이라 눈밑 떨림이나 쥐 나는 증상 완화에 빠른 느낌을 줌</t>
+          <t>저렴하고 실용적인 가격 — 부담 없는 가격으로 구매하여 건강을 챙길 수 있음</t>
         </is>
       </c>
       <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>약간 큰 알약 크기 — 알약 크기가 다소 커서 삼키기 부담스러울 수 있음</t>
+        </is>
+      </c>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
     </row>
     <row r="7" ht="38" customHeight="1">
       <c r="B7" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>멀티비타민/종합비타민</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -5233,12 +5288,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>닥터블릿 푸응 7 Days 슬립앤버닝 14정 7일분</t>
+          <t>대웅제약 멀티비타민 미네랄 30정 30일분</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>닥터블릿</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -5248,30 +5303,34 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=032306284&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000135&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260805/e483TrUWUwCko9CBv1Da032306284_00_00e483TrUWUwCko9CBv1Da.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/2ijoJLmHVT94XXIOZnda600000135_00_002ijoJLmHVT94XXIOZnda.png</t>
         </is>
       </c>
       <c r="I7" t="n">
         <v>4.8</v>
       </c>
       <c r="J7" t="n">
-        <v>191</v>
+        <v>3749</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>취침 전 간편한 복용 — 자기 전 간단히 섭취해 수면 관리에 도움을 받을 수 있음</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr"/>
+          <t>삼키기 쉬운 작은 크기 — 알약 크기가 작아 목 넘김이 수월함</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>저렴하고 실용적인 구성 — 다양한 영양소가 골고루 들어 있어 부담 없이 복용함</t>
+        </is>
+      </c>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>카페인 민감 반응 주의 — 카페인에 민감한 체질의 경우 섭취 시 주의가 필요함</t>
+          <t>한 알당 낮은 함량 — 생각했던 것보다 한 알당 성분 함량이 다소 적음</t>
         </is>
       </c>
       <c r="O7" t="inlineStr"/>
@@ -5280,7 +5339,7 @@
     <row r="8" ht="38" customHeight="1">
       <c r="B8" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -5288,49 +5347,49 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>유한양행 산뜻해질 생유산균 20캡슐 20일분</t>
+          <t>[병풀＆선인장열매] 동국제약 맛있는 센시안 브이캔디 20정 20일분</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>유한양행</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600651654&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=610910968&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260325/BJcWNz19ajlLYaMbOK0e600651654_00_00BJcWNz19ajlLYaMbOK0e.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260409/2cHZmOZUJJcZL1ip2bls610910968_00_002cHZmOZUJJcZL1ip2bls.png</t>
         </is>
       </c>
       <c r="I8" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J8" t="n">
-        <v>1131</v>
+        <v>2632</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>입문용 최적의 가성비 — 저렴한 가격으로 부담 없이 시도하기 좋은 질유산균임</t>
+          <t>붓기 완화 체감 — 섭취 시 붓기가 가라앉고 가벼워지는 느낌을 받음</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>삼키기 편한 초소형 알약 — 캡슐 크기가 작아서 목넘김이 매우 수월함</t>
+          <t>간편한 섭취 방식 — 간단하게 먹을 수 있으며 맛도 적당함</t>
         </is>
       </c>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>용기 내 캡슐 인출 불편 — 포장 용기에서 알약이 한 번에 잘 빠져나오지 않아 불편함</t>
+          <t>체감 효과 미흡 — 사람에 따라 붓기 제거 효과를 전혀 느끼지 못함</t>
         </is>
       </c>
       <c r="O8" t="inlineStr"/>
@@ -5347,47 +5406,47 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>종근당건강 락토핏 골드</t>
+          <t>종근당 데일리와이즈 밀크씨슬 12정 12일분</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>종근당건강</t>
+          <t>종근당</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>2,000원</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=591580521&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=032306204&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260522/0jgRGoNZEcwwrbTgrqVw591580521_00_000jgRGoNZEcwwrbTgrqVw.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260406/RewRRgsZjRVv0Af38IFQ032306204_00_01RewRRgsZjRVv0Af38IFQ.jpg</t>
         </is>
       </c>
       <c r="I9" t="n">
         <v>4.8</v>
       </c>
       <c r="J9" t="n">
-        <v>1753</v>
+        <v>350</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>호불호 없는 친숙한 맛 — 누구나 부담 없이 먹을 수 있는 무난하고 맛있는 분말임</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>휴대 편한 소포장 구성 — 소량 포장이라 여행이나 외출 시 가볍게 챙겨가기 적합함</t>
-        </is>
-      </c>
+          <t>저렴한 가성비 — 가격 부담 없이 간 건강을 챙기기 좋음</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>체감 효능 부족 — 복용 초기 효능을 명확히 체감하기 어려움</t>
+        </is>
+      </c>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
     </row>
@@ -5402,51 +5461,47 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LG생활건강 이너뷰 칼륨밸런스 전해질워터 10포</t>
+          <t>대웅제약 밀크씨슬 6정 6일분</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>이너뷰 바이 리튠</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>1,000원</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=994953534&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000280&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250627/7ii4aNyp1XbM6AH8HjHT994953534_00_007ii4aNyp1XbM6AH8HjHT.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260504/1DUhwiP05cMCEONDxu7B600000280_00_011DUhwiP05cMCEONDxu7B.png</t>
         </is>
       </c>
       <c r="I10" t="n">
         <v>4.8</v>
       </c>
       <c r="J10" t="n">
-        <v>1529</v>
+        <v>331</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>단맛 없는 깔끔한 수분 충전 — 단맛이 없어 질리지 않고 운동 후나 공복에 물처럼 마시기 편함</t>
+          <t>휴대와 단기 복용 용이 — 소용량 구성으로 여행 시나 피곤할 때 단기로 사 먹기 편함</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>부기 완화 및 전해질 균형 — 칼륨과 나트륨 밸런스를 맞춰 속이 무겁지 않고 몸이 가벼워짐</t>
+          <t>가성비 뛰어남 — 다이소 제품으로 가격 부담이 적음</t>
         </is>
       </c>
       <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>포당 다소 애매한 단가 — 다이소 기준 1포당 가격이 생각보다 아주 저렴하진 않음</t>
-        </is>
-      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
     </row>
@@ -5461,52 +5516,56 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>오브맘 활력에너지B 하루구미 30일분</t>
+          <t>[강력한 상쾌함] [신혜선 PICK] 동국제약 프로폴리스 프레쉬볼 스트롱민트 20캡슐 20일분</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>오브맘</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=613602132&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=610911101&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250922/FWBWePRv27KbgtvBHof6613602132_00_01FWBWePRv27KbgtvBHof6.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260907/BQeSyYNH21gmMrEclYYV610911101_00_01BQeSyYNH21gmMrEclYYV.jpg</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J11" t="n">
-        <v>793</v>
+        <v>321</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>간식처럼 챙기는 비타민 — 구미 젤리 형태로 물 없이 맛있고 즐겁게 영양을 챙김</t>
+          <t>강력하고 시원한 민트 향 — 터트리자마자 입안 전체에 상쾌함이 퍼짐</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>활력 개선 및 트러블 완화 — 복용 후 활력이 생기고 입 옆 트는 증상이 완화됨</t>
+          <t>우수한 가성비 — 저렴한 가격에 부담 없이 상쾌함을 유지함</t>
         </is>
       </c>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
-          <t>박카스향 맛의 호불호 — 열대과일 맛보다는 박카스 느낌이 강해 맛에 호불호가 갈림</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr"/>
+          <t>짧은 지속 시간 — 상쾌함의 지속력이 길지 않아 자주 찾게 됨</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>묘한 말캉한 식감 — 입안에서 젤리 같은 묘한 말캉함으로 이질감이 들 수 있음</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr"/>
     </row>
   </sheetData>
@@ -5620,37 +5679,37 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
+          <t>마그네슘</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>혈행</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>루테인/눈건강</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>다이어트/체중관리</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>비타민D</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>멀티비타민/종합비타민</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>혈행</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>마그네슘</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -5677,52 +5736,52 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
+          <t>대웅제약</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>대웅제약</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>대웅제약</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
           <t>동국제약</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>동화약품</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>대웅제약</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>대웅제약</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>자연관</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>닥터블릿</t>
-        </is>
-      </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>유한양행</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>종근당건강</t>
+          <t>종근당</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>이너뷰 바이 리튠</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>오브맘</t>
+          <t>동국제약</t>
         </is>
       </c>
     </row>
@@ -5734,52 +5793,52 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
+          <t>대웅제약 마그네슘 30정 30일분</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>대웅제약 코엔자임 Q10 30캡슐 30일분</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>대웅제약 루테인 30정 30일분</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>[산뜻한 상쾌함] [신혜선 PICK] 동국제약 프로폴리스 프레쉬볼 레몬＆민트 20캡슐 20일분</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>대웅제약 칼슘 마그네슘 비타민D 60정 30일분</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>대웅제약 멀티비타민 미네랄 30정 30일분</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>[병풀＆선인장열매] 동국제약 맛있는 센시안 브이캔디 20정 20일분</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>종근당 데일리와이즈 밀크씨슬 12정 12일분</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>대웅제약 밀크씨슬 6정 6일분</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
           <t>[강력한 상쾌함] [신혜선 PICK] 동국제약 프로폴리스 프레쉬볼 스트롱민트 20캡슐 20일분</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>[식후 혈당] 동화 배러크런치 바나바 요구르트맛 30정 10일분</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>대웅제약 녹차카테킨 30정 30일분</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>대웅제약 코엔자임 Q10 30캡슐 30일분</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>자연관 리프레쉬 마그네슘＆L-테아닌 4병 4일분</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>닥터블릿 푸응 7 Days 슬립앤버닝 14정 7일분</t>
-        </is>
-      </c>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t>유한양행 산뜻해질 생유산균 20캡슐 20일분</t>
-        </is>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>종근당건강 락토핏 골드</t>
-        </is>
-      </c>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t>LG생활건강 이너뷰 칼륨밸런스 전해질워터 10포</t>
-        </is>
-      </c>
-      <c r="L5" s="3" t="inlineStr">
-        <is>
-          <t>오브맘 활력에너지B 하루구미 30일분</t>
         </is>
       </c>
     </row>
@@ -5790,16 +5849,16 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="E6" s="3" t="n">
         <v>4.8</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="G6" s="3" t="n">
         <v>4.8</v>
@@ -5808,7 +5867,7 @@
         <v>4.8</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J6" s="3" t="n">
         <v>4.8</v>
@@ -5817,7 +5876,7 @@
         <v>4.8</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="7">
@@ -5827,34 +5886,34 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>320</v>
+        <v>7031</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>181</v>
+        <v>7498</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>3988</v>
+        <v>4290</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>7489</v>
+        <v>337</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>341</v>
+        <v>3747</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>191</v>
+        <v>3749</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>1131</v>
+        <v>2632</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>1753</v>
+        <v>350</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>1529</v>
+        <v>331</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>793</v>
+        <v>321</v>
       </c>
     </row>
     <row r="8" ht="60" customHeight="1">
@@ -5865,61 +5924,60 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>입안 가득 빠른 상쾌함 — 터뜨리는 순간 강한 민트 향이 퍼져 입안이 즉각 개운해짐
-뛰어난 가성비와 휴대성 — 저렴한 가격으로 언제 어디서나 구취 관리가 가능함</t>
+          <t>합리적인 가격과 성분 — 가격이 저렴하고 알찬 성분 구성으로 꾸준히 먹기 좋음
+빠른 배송 서비스 — 배송 처리가 빨라 빠르게 수령 가능함</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>맛있는 요구르트맛 캔디 — 달콤한 요구르트 맛으로 간식 먹듯이 맛있게 씹어 먹음
-식후 나른함 완화 도움 — 점심 식사 후 졸릴 때 씹어 먹으며 잠을 깨기에 좋음</t>
+          <t>뛰어난 가성비 — 가격 대비 성능이 뛰어나 자주 부담 없이 구매함</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>부담 없는 가성비 가격 — 매우 저렴한 가격에 구매할 수 있어 꾸준히 복용하기 좋음
-식후 체중 유지 관리 — 식사 직후 섭취하여 일상적인 체중 유지에 보조 역할을 함</t>
+          <t>높은 가성비와 만족도 — 저렴한 가격으로 꾸준한 눈 건강 관리에 도움이 됨
+신속한 배송 — 주문 후 배송이 빠름</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>목넘김 편한 적당한 크기 — 알약 크기가 크지 않아 목에 걸리지 않고 편하게 삼켜짐
-오후 시간대 피로 완화 — 한 달간 꾸준히 섭취 시 오후에 덜 지치고 피로가 줄어듦</t>
+          <t>입안의 산뜻한 상쾌함 — 입안이 텁텁할 때 한 개씩 먹으면 개운해짐
+구취 제거 도움 — 입냄새 완화에 유용함</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>부드러운 입면과 숙면 — 취침 전 마시면 잠드는 과정이 부드럽고 기상 시 개운함
-마시는 형태의 빠른 흡수 — 액상형이라 눈밑 떨림이나 쥐 나는 증상 완화에 빠른 느낌을 줌</t>
+          <t>편리한 복합 성분 보충 — 칼슘, 마그네슘, 비타민D를 한 알로 간편하게 섭취함
+저렴하고 실용적인 가격 — 부담 없는 가격으로 구매하여 건강을 챙길 수 있음</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>취침 전 간편한 복용 — 자기 전 간단히 섭취해 수면 관리에 도움을 받을 수 있음</t>
+          <t>삼키기 쉬운 작은 크기 — 알약 크기가 작아 목 넘김이 수월함
+저렴하고 실용적인 구성 — 다양한 영양소가 골고루 들어 있어 부담 없이 복용함</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>입문용 최적의 가성비 — 저렴한 가격으로 부담 없이 시도하기 좋은 질유산균임
-삼키기 편한 초소형 알약 — 캡슐 크기가 작아서 목넘김이 매우 수월함</t>
+          <t>붓기 완화 체감 — 섭취 시 붓기가 가라앉고 가벼워지는 느낌을 받음
+간편한 섭취 방식 — 간단하게 먹을 수 있으며 맛도 적당함</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>호불호 없는 친숙한 맛 — 누구나 부담 없이 먹을 수 있는 무난하고 맛있는 분말임
-휴대 편한 소포장 구성 — 소량 포장이라 여행이나 외출 시 가볍게 챙겨가기 적합함</t>
+          <t>저렴한 가성비 — 가격 부담 없이 간 건강을 챙기기 좋음</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>단맛 없는 깔끔한 수분 충전 — 단맛이 없어 질리지 않고 운동 후나 공복에 물처럼 마시기 편함
-부기 완화 및 전해질 균형 — 칼륨과 나트륨 밸런스를 맞춰 속이 무겁지 않고 몸이 가벼워짐</t>
+          <t>휴대와 단기 복용 용이 — 소용량 구성으로 여행 시나 피곤할 때 단기로 사 먹기 편함
+가성비 뛰어남 — 다이소 제품으로 가격 부담이 적음</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>간식처럼 챙기는 비타민 — 구미 젤리 형태로 물 없이 맛있고 즐겁게 영양을 챙김
-활력 개선 및 트러블 완화 — 복용 후 활력이 생기고 입 옆 트는 증상이 완화됨</t>
+          <t>강력하고 시원한 민트 향 — 터트리자마자 입안 전체에 상쾌함이 퍼짐
+우수한 가성비 — 저렴한 가격에 부담 없이 상쾌함을 유지함</t>
         </is>
       </c>
     </row>
@@ -5929,40 +5987,40 @@
           <t>부정리뷰</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>다소 짧은 향 지속력 — 순간적인 상쾌함은 좋으나 향의 지속 시간이 다소 짧음
-외피 젤리의 이질감 — 입안에 남는 말캉한 캡슐 껍질 식감에 이질감을 느낄 수 있음</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>생각보다 딱딱한 식감 — 정제가 다소 딱딱해 치아에 무리가 갈 수 있어 주의 필요함
-혈당 조절 체감의 한계 — 단기간 섭취로는 뚜렷한 기능성 효과를 체감하기 어려움</t>
-        </is>
-      </c>
+      <c r="C9" s="3" t="inlineStr"/>
+      <c r="D9" s="3" t="inlineStr"/>
       <c r="E9" s="3" t="inlineStr"/>
-      <c r="F9" s="3" t="inlineStr"/>
-      <c r="G9" s="3" t="inlineStr"/>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>입안에 남는 잔여 캡슐 — 캡슐 녹은 후 입안에 껍질만 남고 상쾌함 지속이 짧음
+삼켜야 하는 강한 맛 — 터트려 먹으면 맛이 강해 그냥 삼켜야 하는 불편함이 있음</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>약간 큰 알약 크기 — 알약 크기가 다소 커서 삼키기 부담스러울 수 있음</t>
+        </is>
+      </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>카페인 민감 반응 주의 — 카페인에 민감한 체질의 경우 섭취 시 주의가 필요함</t>
+          <t>한 알당 낮은 함량 — 생각했던 것보다 한 알당 성분 함량이 다소 적음</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>용기 내 캡슐 인출 불편 — 포장 용기에서 알약이 한 번에 잘 빠져나오지 않아 불편함</t>
-        </is>
-      </c>
-      <c r="J9" s="3" t="inlineStr"/>
-      <c r="K9" s="3" t="inlineStr">
-        <is>
-          <t>포당 다소 애매한 단가 — 다이소 기준 1포당 가격이 생각보다 아주 저렴하진 않음</t>
-        </is>
-      </c>
+          <t>체감 효과 미흡 — 사람에 따라 붓기 제거 효과를 전혀 느끼지 못함</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>체감 효능 부족 — 복용 초기 효능을 명확히 체감하기 어려움</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr"/>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>박카스향 맛의 호불호 — 열대과일 맛보다는 박카스 느낌이 강해 맛에 호불호가 갈림</t>
+          <t>짧은 지속 시간 — 상쾌함의 지속력이 길지 않아 자주 찾게 됨
+묘한 말캉한 식감 — 입안에서 젤리 같은 묘한 말캉함으로 이질감이 들 수 있음</t>
         </is>
       </c>
     </row>
@@ -5979,47 +6037,47 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
+          <t>5,000원</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
           <t>3,000원</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>3,000원</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
         <is>
           <t>5,000원</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
+      <c r="H10" s="3" t="inlineStr">
         <is>
           <t>5,000원</t>
         </is>
       </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>5,000원</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>5,000원</t>
-        </is>
-      </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>2,000원</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>1,000원</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
     </row>
@@ -6198,7 +6256,7 @@
     <row r="2" ht="38" customHeight="1">
       <c r="B2" t="inlineStr">
         <is>
-          <t>피부/미용</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -6206,27 +6264,27 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>[10일콜라겐/모공,목주름/PDRN] 라이필 더마콜라겐 시그니처RN (10일분)</t>
+          <t>[10/21 하루특가] 칼로 스탑/컨트롤 PLUS 15포 2종</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>라이필</t>
+          <t>칼로(Kalo)</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>15,840원</t>
+          <t>8,500원</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000259411&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=1</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000186228&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=1</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0025/A00000025941123ko.png?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0018/A00000018622875ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -6249,27 +6307,27 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>리쥬란 이너닷 DNA 글로우 젤리(단품/기획)</t>
+          <t>[올영단독 증량기획] 셀트리온 홀드잇 30정 기획 (+7일 추가 증정)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>리쥬란</t>
+          <t>이너랩</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>24,900원</t>
+          <t>17,900원</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000258641&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=2</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000225470&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=2</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0025/A00000025864120ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0022/A00000022547089ko.png?l=ko</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -6292,42 +6350,54 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>[올영단독 증량기획] 셀트리온 홀드잇 30정 기획 (+7일 추가 증정)</t>
+          <t>리쥬란 이너닷 DNA 글로우 젤리(단품/기획)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>이너랩</t>
+          <t>리쥬란</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>17,900원</t>
+          <t>24,900원</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000225470&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=3</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000258641&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=3</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0022/A00000022547089ko.png?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0025/A00000025864120ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>맛있는 젤리 형태 — 탱글하고 쫀득한 청포도 사과맛 젤리로 간식처럼 먹기 좋음</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>뛰어난 휴대성 — 한 포씩 낱개 포장되어 외출 시 챙겨 다니기 편함</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>높은 가격 부담 — 사용감은 좋으나 비싼 가격 때문에 재구매가 망설여짐</t>
+        </is>
+      </c>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
     </row>
     <row r="5" ht="38" customHeight="1">
       <c r="B5" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -6335,31 +6405,35 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>[한선화 PICK] 프로뉴트리션 듀얼플랜 다이어트 유산균 14포</t>
+          <t>지노마스터 질유산균 30캡슐 기획 (+보라지유 5일분) (1개월분)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>프로뉴트리션</t>
+          <t>지노마스터</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>35,800원</t>
+          <t>27,400원</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000205496&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=4</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000244929&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=4</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020549621ko.jpg?l=ko</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024492948ko.jpg?l=ko</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J5" t="n">
+        <v>26053</v>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
@@ -6370,7 +6444,7 @@
     <row r="6" ht="38" customHeight="1">
       <c r="B6" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>멀티비타민/종합비타민</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -6378,35 +6452,51 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>판도라 브이펌킨티 14개입 (2주분)</t>
+          <t>오쏘몰 이뮨 멀티비타민&amp;미네랄 14+1입</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>판도라</t>
+          <t>오쏘몰</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>22,700원</t>
+          <t>54,900원</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000001001703&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=5</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000193086&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=5</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0100/A00000100170303ko.png?l=ko</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0019/A00000019308652ko.jpg?l=ko</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J6" t="n">
+        <v>41465</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>확실한 피로 해소 — 지친 직장인이나 수험생의 피로 회복에 효과적임</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>맛있는 액상 제형 — 탄산수 등에 타 먹으면 상큼한 에이드처럼 즐길 수 있음</t>
+        </is>
+      </c>
       <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>비싼 가격대 — 영양제 가격이 높은 편이라 구매 부담이 존재함</t>
+        </is>
+      </c>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
     </row>
@@ -6446,8 +6536,16 @@
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>장 건강 및 면역력 케어 — 장 건강 관리를 통해 면역력 유지에 큰 도움을 줌</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>간편한 하루 1캡슐 — 아침 물과 함께 1캡슐씩 복용하여 장기간 관리하기 편리함</t>
+        </is>
+      </c>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
@@ -6456,7 +6554,7 @@
     <row r="8" ht="38" customHeight="1">
       <c r="B8" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -6464,45 +6562,33 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>지노마스터 질유산균 30캡슐 기획 (+보라지유 5일분) (1개월분)</t>
+          <t>[한선화 PICK] 프로뉴트리션 듀얼플랜 다이어트 유산균 14포</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>지노마스터</t>
+          <t>프로뉴트리션</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>27,400원</t>
+          <t>35,800원</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000244929&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=7</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000205496&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=7</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024492948ko.jpg?l=ko</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="J8" t="n">
-        <v>26051</v>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>초소형 캡슐의 편한 목넘김 — 캡슐 크기가 170mg으로 매우 작고 가벼워 쉽게 삼켜짐</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>질과 장의 동시 케어 — 기능성 원료를 통해 질과 장 건강을 한 번에 관리 가능함</t>
-        </is>
-      </c>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020549621ko.jpg?l=ko</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
@@ -6519,7 +6605,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>오쏘몰 이뮨 멀티비타민&amp;미네랄 14+1입</t>
+          <t>오쏘몰 이뮨 멀티비타민&amp;미네랄 30입 (1개월분)</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -6529,48 +6615,44 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>54,900원</t>
+          <t>109,000원</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000193086&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=8</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000207974&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=8</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0019/A00000019308652ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020797409ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I9" t="n">
         <v>4.9</v>
       </c>
       <c r="J9" t="n">
-        <v>41460</v>
+        <v>41830</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>체감되는 피로 회복 효과 — 지친 직장인과 수험생의 체력 충전과 피로 개선에 뛰어남</t>
+          <t>물 없이 언제나 복용 — 알약과 액상 일체형으로 물 없이 어디서나 섭취함</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>탄산수 조합 에이드 음용 — 진한 액상을 탄산수에 타서 상큼한 음료처럼 즐기기 좋음</t>
+          <t>체력 증진 완화 체감 — 섭취 후 체력적인 차이가 명확히 느껴져 효과적임</t>
         </is>
       </c>
       <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>다소 부담스러운 가격대 — 효능은 우수하나 정가 기준 가격대가 비싸서 부담스러움</t>
-        </is>
-      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
     </row>
     <row r="10" ht="38" customHeight="1">
       <c r="B10" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>비타민C/항산화</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -6578,47 +6660,35 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>코자아 식물성 멜라토닌 함유 젤리/드링크 (단품/기획)</t>
+          <t>[베러PICK] 온리추얼 비타민C 글로우업 트리플 7포+1포 (8일분)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>코자아</t>
+          <t>온리추얼</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>32,900원</t>
+          <t>17,900원</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000236755&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=9</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000263899&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=9</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0023/A00000023675540ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0026/A00000026389913ko.png?l=ko</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>빠른 입면과 수면 질 개선 — 취침 전 섭취 시 쉽게 잠들고 다음 날 아침이 개운해짐</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>맛있는 포도 젤리 제형 — 마이구미 같은 달콤한 맛으로 거부감 없이 챙겨 먹기 좋음</t>
-        </is>
-      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>섭취 후 양치질 번거로움 — 자기 전 젤리를 씹어 먹은 뒤 다시 양치해야 하는 불편함이 있음</t>
-        </is>
-      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
     </row>
@@ -6633,35 +6703,31 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>CJ BYOCORE 바나나효소 30포 + 키캡 키링 (1개월분)</t>
+          <t>덴프스 덴마크 유산균이야기 우먼 2개월분(질유산균) + 철분 헤모케어 3포 증정</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>바이오코어유산균</t>
+          <t>덴프스</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>15,900원</t>
+          <t>31,400원</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000261662&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=10</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000202658&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=10</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0026/A00000026166204ko.jpg?l=ko</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="J11" t="n">
-        <v>19</v>
-      </c>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020265829ko.jpg?l=ko</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
@@ -6780,7 +6846,7 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>피부/미용</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
@@ -6795,24 +6861,24 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
+          <t>프로바이오틱스/유산균</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>멀티비타민/종합비타민</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>프로바이오틱스/유산균</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
           <t>다이어트/체중관리</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>프로바이오틱스/유산균</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>프로바이오틱스/유산균</t>
-        </is>
-      </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
           <t>멀티비타민/종합비타민</t>
@@ -6820,7 +6886,7 @@
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>비타민C/항산화</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
@@ -6837,52 +6903,52 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>라이필</t>
+          <t>칼로(Kalo)</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
+          <t>이너랩</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
           <t>리쥬란</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>이너랩</t>
-        </is>
-      </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
+          <t>지노마스터</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>오쏘몰</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>덴프스</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
           <t>프로뉴트리션</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>판도라</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>오쏘몰</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>온리추얼</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
         <is>
           <t>덴프스</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>지노마스터</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>오쏘몰</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>코자아</t>
-        </is>
-      </c>
-      <c r="L4" s="3" t="inlineStr">
-        <is>
-          <t>바이오코어유산균</t>
         </is>
       </c>
     </row>
@@ -6894,52 +6960,52 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>[10일콜라겐/모공,목주름/PDRN] 라이필 더마콜라겐 시그니처RN (10일분)</t>
+          <t>[10/21 하루특가] 칼로 스탑/컨트롤 PLUS 15포 2종</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
+          <t>[올영단독 증량기획] 셀트리온 홀드잇 30정 기획 (+7일 추가 증정)</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
           <t>리쥬란 이너닷 DNA 글로우 젤리(단품/기획)</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>[올영단독 증량기획] 셀트리온 홀드잇 30정 기획 (+7일 추가 증정)</t>
-        </is>
-      </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
+          <t>지노마스터 질유산균 30캡슐 기획 (+보라지유 5일분) (1개월분)</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>오쏘몰 이뮨 멀티비타민&amp;미네랄 14+1입</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>[덴프스] 덴마크 유산균이야기 30캡슐 1+1 기획 (+트루바이타민 3포 증정)</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
           <t>[한선화 PICK] 프로뉴트리션 듀얼플랜 다이어트 유산균 14포</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>판도라 브이펌킨티 14개입 (2주분)</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>[덴프스] 덴마크 유산균이야기 30캡슐 1+1 기획 (+트루바이타민 3포 증정)</t>
-        </is>
-      </c>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t>지노마스터 질유산균 30캡슐 기획 (+보라지유 5일분) (1개월분)</t>
-        </is>
-      </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>오쏘몰 이뮨 멀티비타민&amp;미네랄 14+1입</t>
+          <t>오쏘몰 이뮨 멀티비타민&amp;미네랄 30입 (1개월분)</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>코자아 식물성 멜라토닌 함유 젤리/드링크 (단품/기획)</t>
+          <t>[베러PICK] 온리추얼 비타민C 글로우업 트리플 7포+1포 (8일분)</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>CJ BYOCORE 바나나효소 30포 + 키캡 키링 (1개월분)</t>
+          <t>덴프스 덴마크 유산균이야기 우먼 2개월분(질유산균) + 철분 헤모케어 3포 증정</t>
         </is>
       </c>
     </row>
@@ -6952,19 +7018,19 @@
       <c r="C6" s="3" t="inlineStr"/>
       <c r="D6" s="3" t="inlineStr"/>
       <c r="E6" s="3" t="inlineStr"/>
-      <c r="F6" s="3" t="inlineStr"/>
-      <c r="G6" s="3" t="inlineStr"/>
+      <c r="F6" s="3" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>4.9</v>
+      </c>
       <c r="H6" s="3" t="inlineStr"/>
-      <c r="I6" s="3" t="n">
-        <v>4.9</v>
-      </c>
+      <c r="I6" s="3" t="inlineStr"/>
       <c r="J6" s="3" t="n">
         <v>4.9</v>
       </c>
       <c r="K6" s="3" t="inlineStr"/>
-      <c r="L6" s="3" t="n">
-        <v>4.7</v>
-      </c>
+      <c r="L6" s="3" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="B7" s="1" t="inlineStr">
@@ -6975,19 +7041,19 @@
       <c r="C7" s="3" t="inlineStr"/>
       <c r="D7" s="3" t="inlineStr"/>
       <c r="E7" s="3" t="inlineStr"/>
-      <c r="F7" s="3" t="inlineStr"/>
-      <c r="G7" s="3" t="inlineStr"/>
+      <c r="F7" s="3" t="n">
+        <v>26053</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>41465</v>
+      </c>
       <c r="H7" s="3" t="inlineStr"/>
-      <c r="I7" s="3" t="n">
-        <v>26051</v>
-      </c>
+      <c r="I7" s="3" t="inlineStr"/>
       <c r="J7" s="3" t="n">
-        <v>41460</v>
+        <v>41830</v>
       </c>
       <c r="K7" s="3" t="inlineStr"/>
-      <c r="L7" s="3" t="n">
-        <v>19</v>
-      </c>
+      <c r="L7" s="3" t="inlineStr"/>
     </row>
     <row r="8" ht="60" customHeight="1">
       <c r="B8" s="1" t="inlineStr">
@@ -6997,28 +7063,33 @@
       </c>
       <c r="C8" s="3" t="inlineStr"/>
       <c r="D8" s="3" t="inlineStr"/>
-      <c r="E8" s="3" t="inlineStr"/>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>맛있는 젤리 형태 — 탱글하고 쫀득한 청포도 사과맛 젤리로 간식처럼 먹기 좋음
+뛰어난 휴대성 — 한 포씩 낱개 포장되어 외출 시 챙겨 다니기 편함</t>
+        </is>
+      </c>
       <c r="F8" s="3" t="inlineStr"/>
-      <c r="G8" s="3" t="inlineStr"/>
-      <c r="H8" s="3" t="inlineStr"/>
-      <c r="I8" s="3" t="inlineStr">
-        <is>
-          <t>초소형 캡슐의 편한 목넘김 — 캡슐 크기가 170mg으로 매우 작고 가벼워 쉽게 삼켜짐
-질과 장의 동시 케어 — 기능성 원료를 통해 질과 장 건강을 한 번에 관리 가능함</t>
-        </is>
-      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>확실한 피로 해소 — 지친 직장인이나 수험생의 피로 회복에 효과적임
+맛있는 액상 제형 — 탄산수 등에 타 먹으면 상큼한 에이드처럼 즐길 수 있음</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>장 건강 및 면역력 케어 — 장 건강 관리를 통해 면역력 유지에 큰 도움을 줌
+간편한 하루 1캡슐 — 아침 물과 함께 1캡슐씩 복용하여 장기간 관리하기 편리함</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr"/>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>체감되는 피로 회복 효과 — 지친 직장인과 수험생의 체력 충전과 피로 개선에 뛰어남
-탄산수 조합 에이드 음용 — 진한 액상을 탄산수에 타서 상큼한 음료처럼 즐기기 좋음</t>
-        </is>
-      </c>
-      <c r="K8" s="3" t="inlineStr">
-        <is>
-          <t>빠른 입면과 수면 질 개선 — 취침 전 섭취 시 쉽게 잠들고 다음 날 아침이 개운해짐
-맛있는 포도 젤리 제형 — 마이구미 같은 달콤한 맛으로 거부감 없이 챙겨 먹기 좋음</t>
-        </is>
-      </c>
+          <t>물 없이 언제나 복용 — 알약과 액상 일체형으로 물 없이 어디서나 섭취함
+체력 증진 완화 체감 — 섭취 후 체력적인 차이가 명확히 느껴져 효과적임</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr"/>
       <c r="L8" s="3" t="inlineStr"/>
     </row>
     <row r="9">
@@ -7029,21 +7100,21 @@
       </c>
       <c r="C9" s="3" t="inlineStr"/>
       <c r="D9" s="3" t="inlineStr"/>
-      <c r="E9" s="3" t="inlineStr"/>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>높은 가격 부담 — 사용감은 좋으나 비싼 가격 때문에 재구매가 망설여짐</t>
+        </is>
+      </c>
       <c r="F9" s="3" t="inlineStr"/>
-      <c r="G9" s="3" t="inlineStr"/>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>비싼 가격대 — 영양제 가격이 높은 편이라 구매 부담이 존재함</t>
+        </is>
+      </c>
       <c r="H9" s="3" t="inlineStr"/>
       <c r="I9" s="3" t="inlineStr"/>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>다소 부담스러운 가격대 — 효능은 우수하나 정가 기준 가격대가 비싸서 부담스러움</t>
-        </is>
-      </c>
-      <c r="K9" s="3" t="inlineStr">
-        <is>
-          <t>섭취 후 양치질 번거로움 — 자기 전 젤리를 씹어 먹은 뒤 다시 양치해야 하는 불편함이 있음</t>
-        </is>
-      </c>
+      <c r="J9" s="3" t="inlineStr"/>
+      <c r="K9" s="3" t="inlineStr"/>
       <c r="L9" s="3" t="inlineStr"/>
     </row>
     <row r="10">
@@ -7054,52 +7125,52 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>15,840원</t>
+          <t>8,500원</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
+          <t>17,900원</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
           <t>24,900원</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>27,400원</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>54,900원</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>30,400원</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>35,800원</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>109,000원</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
         <is>
           <t>17,900원</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>35,800원</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>22,700원</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>30,400원</t>
-        </is>
-      </c>
-      <c r="I10" s="3" t="inlineStr">
-        <is>
-          <t>27,400원</t>
-        </is>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>54,900원</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="inlineStr">
-        <is>
-          <t>32,900원</t>
-        </is>
-      </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>15,900원</t>
+          <t>31,400원</t>
         </is>
       </c>
     </row>
@@ -7187,7 +7258,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7235,13 +7306,13 @@
         <v>32.5</v>
       </c>
       <c r="D2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F2" t="n">
         <v>3</v>
-      </c>
-      <c r="E2" t="n">
-        <v>6</v>
-      </c>
-      <c r="F2" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -7251,19 +7322,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C3" t="n">
-        <v>22.5</v>
+        <v>27.5</v>
       </c>
       <c r="D3" t="n">
         <v>8</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -7273,16 +7344,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C4" t="n">
-        <v>20</v>
+        <v>12.5</v>
       </c>
       <c r="D4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
         <v>1</v>
@@ -7295,16 +7366,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C5" t="n">
-        <v>10</v>
+        <v>7.5</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
         <v>3</v>
@@ -7313,7 +7384,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>피부/미용</t>
+          <t>비타민C/항산화</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -7335,7 +7406,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>홍삼/인삼</t>
+          <t>피부/미용</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -7357,7 +7428,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>비타민C/항산화</t>
+          <t>루테인/눈건강</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -7367,10 +7438,10 @@
         <v>2.5</v>
       </c>
       <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
         <v>1</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -7401,7 +7472,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>마그네슘</t>
+          <t>홍삼/인삼</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -7411,12 +7482,56 @@
         <v>2.5</v>
       </c>
       <c r="D10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" t="n">
         <v>0</v>
       </c>
-      <c r="E10" t="n">
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>비타민D</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
         <v>1</v>
       </c>
-      <c r="F10" t="n">
+      <c r="C11" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>마그네슘</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
         <v>0</v>
       </c>
     </row>
